--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,7 +273,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}onc-oral-gate:Safety Rule: If patient is Nil By Mouth (NBM), Oral Care frequency must be specified. {value.coding.where(code = 'nbm').exists() implies component.where(code.coding.code = 'frequency').exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1368,6 +1368,10 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:code}
+</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1438,6 +1442,47 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex</t>
+  </si>
+  <si>
+    <t>empathyIndex</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.id</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://opennursingcoreig.com/CodeSystem/onc-observation-codes"/&gt;
+    &lt;code value="empathy-index"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.value[x]</t>
+  </si>
+  <si>
+    <t>https://opennursingcoreig.com/ValueSet/onc-empathy-index-vs</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:empathyIndex.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -1746,12 +1791,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.0546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.25" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1774,7 +1819,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -6997,13 +7042,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -7061,16 +7106,14 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>423</v>
@@ -7094,10 +7137,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7108,10 +7151,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7226,10 +7269,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7346,10 +7389,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7468,10 +7511,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7497,13 +7540,13 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>207</v>
@@ -7555,7 +7598,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7573,7 +7616,7 @@
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>214</v>
@@ -7590,10 +7633,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7616,16 +7659,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>275</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>277</v>
@@ -7677,7 +7720,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7695,7 +7738,7 @@
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>280</v>
@@ -7712,10 +7755,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7741,13 +7784,13 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>287</v>
@@ -7799,7 +7842,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7834,10 +7877,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7921,7 +7964,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7956,10 +7999,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7985,10 +8028,10 @@
         <v>80</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>354</v>
@@ -8043,7 +8086,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8076,8 +8119,1100 @@
         <v>18</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y58" s="2"/>
+      <c r="Z58" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP52">
+  <autoFilter ref="A1:AP61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8087,7 +9222,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,8 +673,9 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://opennursingcoreig.com/CodeSystem/onc-observation-codes"/&gt;
-    &lt;code value="oral-care"/&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="30175009"/&gt;
+    &lt;display value="Initial oral examination"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-care-assessment.xlsx
+++ b/StructureDefinition-onc-oral-care-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
